--- a/mapping/PDTD_DTM/Mapping_DIM_RLOS_APPLICATION.xlsx
+++ b/mapping/PDTD_DTM/Mapping_DIM_RLOS_APPLICATION.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping'!$A$5:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping'!$A$6:$E$71</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
@@ -225,7 +225,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -302,9 +302,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -355,9 +352,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -377,7 +371,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="F5" authorId="0" shapeId="0">
+    <comment ref="F6" authorId="0" shapeId="0">
       <text>
         <t>Admin:
  (Chir lấy các tài khoản là tài khoản thuộc phân hệ MG, LD, AC - Thấu chi, AZ - Defer)</t>
@@ -678,13 +672,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="29.6640625" customWidth="1" style="7" min="1" max="1"/>
     <col width="20.5" customWidth="1" style="7" min="2" max="2"/>
     <col width="27.6640625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="37" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="52.1640625" customWidth="1" style="2" min="4" max="4"/>
     <col width="50.33203125" customWidth="1" style="7" min="5" max="5"/>
     <col width="48.5" customWidth="1" style="2" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="7" min="7" max="16384"/>
@@ -701,12 +695,12 @@
           <t>DIM_RLOS_APPLICATION</t>
         </is>
       </c>
-      <c r="E1" s="43" t="inlineStr">
+      <c r="E1" s="42" t="inlineStr">
         <is>
           <t>STG_DIM_RLOS_APPLICATION AS A</t>
         </is>
       </c>
-      <c r="F1" s="43" t="n"/>
+      <c r="F1" s="42" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -719,1868 +713,1882 @@
           <t>Relay/merge từ STG_DTM.STG_DIM_RLOS_APPLICATION sang PDTD_DTM theo delta EFF/EXP (merge-by-key, không aggregation thêm)</t>
         </is>
       </c>
-      <c r="E2" s="43" t="n"/>
-      <c r="F2" s="43" t="n"/>
+      <c r="E2" s="42" t="n"/>
+      <c r="F2" s="42" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Primary Key</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Bao gồm các trường màu đỏ</t>
-        </is>
-      </c>
-      <c r="E3" s="43" t="n"/>
-      <c r="F3" s="43" t="n"/>
+          <t>DIMENSION_KEY</t>
+        </is>
+      </c>
+      <c r="E3" s="42" t="n"/>
+      <c r="F3" s="42" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="E4" s="43" t="n"/>
-      <c r="F4" s="43" t="n"/>
-    </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Business Key</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="42" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="E5" s="42" t="n"/>
+      <c r="F5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Column name</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Column type</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Item Name</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>How to mapping RLOS</t>
         </is>
       </c>
-      <c r="F5" s="25" t="n"/>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="23" t="n"/>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="F6" s="25" t="n"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="23" t="n"/>
+      <c r="B7" s="23" t="n"/>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Điều kiện lấy dữ liệu</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>(A.EFF_DATE = v_batch_date OR (A.EXP_DATE &gt;= v_prev_date AND A.EXP_DATE &lt; v_batch_date))</t>
         </is>
       </c>
-      <c r="F6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="F7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Surrogate Key</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>PK — Driving: STG_DIM_RLOS_APPLICATION. Merge theo DIMENSION_KEY vào PDTD_DTM: chỉ lấy bản ghi từ STG_DTM vừa mở hiệu lực đúng v_batch_date, hoặc vừa đóng hiệu lực trong khoảng [v_prev_date, v_batch_date), rồi UPSERT theo key — không phải full reload.</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>PK — Driving: STG_DIM_RLOS_APPLICATION</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>A.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="F8" s="30" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>Khóa tham chiếu DIM_RLOS_APPLICATION</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Bằng đúng DIMENSION_KEY cùng dòng</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>A.APPLICATION_SK</t>
         </is>
       </c>
-      <c r="F8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="F9" s="30" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>WI_NAME</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng RLOS</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Business key — mã hồ sơ tín dụng RLOS</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F9" s="31" t="n"/>
-    </row>
-    <row r="10" ht="17" customFormat="1" customHeight="1" s="5">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="F10" s="30" t="n"/>
+    </row>
+    <row r="11" ht="15" customFormat="1" customHeight="1" s="5">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>LOANCASEID</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Mã khoản vay</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Mã khoản vay gắn với hồ sơ</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>A.LOANCASEID</t>
         </is>
       </c>
-      <c r="F10" s="31" t="n"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="F11" s="30" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>STREAM</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Luồng nghiệp vụ</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Luồng nghiệp vụ của hồ sơ</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>A.STREAM</t>
         </is>
       </c>
-      <c r="F11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="44" t="inlineStr">
+      <c r="F12" s="30" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>POLICY</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Chính sách tín dụng</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Chính sách tín dụng áp dụng cho hồ sơ</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>A.POLICY</t>
         </is>
       </c>
-      <c r="F12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
+      <c r="F13" s="30" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>CAMPAIGN</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>Chương trình bán</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Chương trình bán áp dụng cho hồ sơ</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>A.CAMPAIGN</t>
         </is>
       </c>
-      <c r="F13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="44" t="inlineStr">
+      <c r="F14" s="30" t="n"/>
+    </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>PROOF_OF_INCOME</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>Hình thức chứng minh thu nhập</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Hình thức chứng minh thu nhập — PHÁI SINH tại PDTD_DTM (review 2026-09-26)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>CASE WHEN A.PROOF_OF_INCOME = 'proofincome01' THEN 'CHUNGTU_CHUNGMINH_THUNHAP' WHEN A.PROOF_OF_INCOME = 'proofincome02' THEN 'BANGKE_THUNHAP' END</t>
         </is>
       </c>
-      <c r="F14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="F15" s="30" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>COLL_REQUIRE</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>Yêu cầu tài sản bảo đảm</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Sản phẩm có yêu cầu tài sản bảo đảm hay không — PHÁI SINH tại PDTD_DTM (review 2026-09-26)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>CASE WHEN A.COLL_REQUIRE = 'true' THEN 'YES' ELSE 'NO' END</t>
         </is>
       </c>
-      <c r="F15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="F16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>IS_SEC_PRODUCT</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>Có sản phẩm phụ</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Hồ sơ có sản phẩm phụ đi kèm hay không</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>A.IS_SEC_PRODUCT</t>
         </is>
       </c>
-      <c r="F16" s="31" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="44" t="inlineStr">
+      <c r="F17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>DEVIATION_FLAG</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>Có ngoại lệ chính sách</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Hồ sơ có ngoại lệ chính sách hay không</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>A.DEVIATION_FLAG</t>
         </is>
       </c>
-      <c r="F17" s="31" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
+      <c r="F18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>CREATE_EMPLOYEE_CODE</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>Mã cán bộ quản lý hồ sơ</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Mã cán bộ quản lý hồ sơ</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>A.CREATE_EMPLOYEE_CODE</t>
         </is>
       </c>
-      <c r="F18" s="31" t="n"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
+      <c r="F19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>CREATE_EMPLOYEE_NAME</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>Tên cán bộ quản lý hồ sơ</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Tên cán bộ quản lý hồ sơ</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>A.CREATE_EMPLOYEE_NAME</t>
         </is>
       </c>
-      <c r="F19" s="31" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="F20" s="30" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>CREATION_DATE</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>Ngày khởi tạo hồ sơ</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Ngày khởi tạo hồ sơ</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>A.CREATION_DATE</t>
         </is>
       </c>
-      <c r="F20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="44" t="inlineStr">
+      <c r="F21" s="30" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>APPLICATION_DATE</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>Ngày khởi tạo theo form</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Ngày khởi tạo hồ sơ khai theo form</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>A.APPLICATION_DATE</t>
         </is>
       </c>
-      <c r="F21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="F22" s="30" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>RESULT_MAIN_CARD_ID</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>Mã thẻ chính (T24)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Mã thẻ chính do hệ thẻ (T24) trả về</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>A.RESULT_MAIN_CARD_ID</t>
         </is>
       </c>
-      <c r="F22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="44" t="inlineStr">
+      <c r="F23" s="30" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>APP_GRP</t>
         </is>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>Cấp thẩm quyền phê duyệt</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Cấp thẩm quyền phê duyệt của hồ sơ</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>A.APP_GRP</t>
         </is>
       </c>
-      <c r="F23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="44" t="inlineStr">
+      <c r="F24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>LAST_APPROVAL_DATE</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <t>Ngày phê duyệt gần nhất</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Ngày phê duyệt gần nhất của hồ sơ</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>A.LAST_APPROVAL_DATE</t>
         </is>
       </c>
-      <c r="F24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="F25" s="30" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>CUSTOMER_NAME</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(150)</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>Tên khách hàng vay chính</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Tên khách hàng đứng tên vay chính của hồ sơ</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>A.CUSTOMER_NAME</t>
         </is>
       </c>
-      <c r="F25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="44" t="inlineStr">
+      <c r="F26" s="30" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>APPROVAL_CONDITION</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
         <is>
           <t>Nhóm/cấp phê duyệt</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Nhóm/cấp phê duyệt áp dụng cho hồ sơ, cùng bộ mã với APP_GRP nhưng ghi nhận trực tiếp trên EXTTABLE</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>A.APPROVAL_CONDITION</t>
         </is>
       </c>
-      <c r="F26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="44" t="inlineStr">
+      <c r="F27" s="30" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>APPROVER_TYPE</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>Loại cấp phê duyệt</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Loại cấp phê duyệt xử lý hồ sơ</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>A.APPROVER_TYPE</t>
         </is>
       </c>
-      <c r="F27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="44" t="inlineStr">
+      <c r="F28" s="30" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>APP_STATUS</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C28" s="31" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>Trạng thái hồ sơ</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Trạng thái hồ sơ</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>A.APP_STATUS</t>
         </is>
       </c>
-      <c r="F28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="44" t="inlineStr">
+      <c r="F29" s="30" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>RMEMAILID</t>
         </is>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(250)</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>Email cán bộ RM</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Email cán bộ quan hệ khách hàng (RM) phụ trách</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>A.RMEMAILID</t>
         </is>
       </c>
-      <c r="F29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="44" t="inlineStr">
+      <c r="F30" s="30" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>REMARKS</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C30" s="31" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Ghi chú, dữ liệu HTML thô, rất ít khi có dữ liệu</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>A.REMARKS</t>
         </is>
       </c>
-      <c r="F30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="44" t="inlineStr">
+      <c r="F31" s="30" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>ZONE</t>
         </is>
       </c>
-      <c r="B31" s="27" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
+      <c r="C32" s="30" t="inlineStr">
         <is>
           <t>Vùng miền quản lý tự khai</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Vùng miền quản lý tự khai theo hồ sơ (BC1/BC2.ZONE)</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>A.ZONE</t>
         </is>
       </c>
-      <c r="F31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="44" t="inlineStr">
+      <c r="F32" s="30" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>SALE_TYPE</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>Kênh bán hàng</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Kênh bán hàng</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>A.SALE_TYPE</t>
         </is>
       </c>
-      <c r="F32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="44" t="inlineStr">
+      <c r="F33" s="30" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>BROKER_TYPE</t>
         </is>
       </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C33" s="31" t="inlineStr">
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>Loại đối tác giới thiệu</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Loại đối tác giới thiệu</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>A.BROKER_TYPE</t>
         </is>
       </c>
-      <c r="F33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="44" t="inlineStr">
+      <c r="F34" s="30" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>BROKER_ID</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C34" s="31" t="inlineStr">
+      <c r="C35" s="30" t="inlineStr">
         <is>
           <t>Mã đối tác giới thiệu</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Mã đối tác giới thiệu</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>A.BROKER_ID</t>
         </is>
       </c>
-      <c r="F34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="44" t="inlineStr">
+      <c r="F35" s="30" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>BROKER_NAME</t>
         </is>
       </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C35" s="31" t="inlineStr">
+      <c r="C36" s="30" t="inlineStr">
         <is>
           <t>Tên đối tác giới thiệu</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Tên đối tác giới thiệu</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>A.BROKER_NAME</t>
         </is>
       </c>
-      <c r="F35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="44" t="inlineStr">
+      <c r="F36" s="30" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>ACC_OFFICER</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C36" s="31" t="inlineStr">
+      <c r="C37" s="30" t="inlineStr">
         <is>
           <t>Mã Account Officer</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Mã nhân viên quan hệ khách hàng (Account Officer) phụ trách hồ sơ</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>A.ACC_OFFICER</t>
         </is>
       </c>
-      <c r="F36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="44" t="inlineStr">
+      <c r="F37" s="30" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>ACCOUNT_OFFICER_NAME</t>
         </is>
       </c>
-      <c r="B37" s="27" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C37" s="31" t="inlineStr">
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>Tên Account Officer</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Tên Account Officer phụ trách hồ sơ</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>A.ACCOUNT_OFFICER_NAME</t>
         </is>
       </c>
-      <c r="F37" s="31" t="n"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="44" t="inlineStr">
+      <c r="F38" s="30" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>EXISTING_CUSTOMER</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C38" s="31" t="inlineStr">
+      <c r="C39" s="30" t="inlineStr">
         <is>
           <t>Cờ khách hàng hiện hữu</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>Cờ khách hàng hiện hữu tại thời điểm nộp hồ sơ</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>A.EXISTING_CUSTOMER</t>
         </is>
       </c>
-      <c r="F38" s="31" t="n"/>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="44" t="inlineStr">
+      <c r="F39" s="30" t="n"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>APPLICANT_CIF</t>
         </is>
       </c>
-      <c r="B39" s="27" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C39" s="31" t="inlineStr">
+      <c r="C40" s="30" t="inlineStr">
         <is>
           <t>Mã CIF khách hàng</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Mã CIF khách hàng (định danh ngân hàng lõi) tại thời điểm hồ sơ</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>A.APPLICANT_CIF</t>
         </is>
       </c>
-      <c r="F39" s="31" t="n"/>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="44" t="inlineStr">
+      <c r="F40" s="30" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>KYC1</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C40" s="31" t="inlineStr">
+      <c r="C41" s="30" t="inlineStr">
         <is>
           <t>Đơn vị/khối đang xử lý</t>
         </is>
       </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>Đơn vị/khối đang xử lý hồ sơ tại thời điểm ghi nhận</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>A.KYC1</t>
         </is>
       </c>
-      <c r="F40" s="31" t="n"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="44" t="inlineStr">
+      <c r="F41" s="30" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>INTEREST_RATE_PCT</t>
         </is>
       </c>
-      <c r="B41" s="27" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C41" s="31" t="inlineStr">
+      <c r="C42" s="30" t="inlineStr">
         <is>
           <t>Lãi suất phê duyệt</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>Lãi suất phê duyệt (%) — lưu SCD1</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>A.INTEREST_RATE_PCT</t>
         </is>
       </c>
-      <c r="F41" s="31" t="n"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="44" t="inlineStr">
+      <c r="F42" s="30" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>LOAN_TO_VALUE</t>
         </is>
       </c>
-      <c r="B42" s="27" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C42" s="31" t="inlineStr">
+      <c r="C43" s="30" t="inlineStr">
         <is>
           <t>Tỷ lệ cho vay/TSBĐ</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>Tỷ lệ cho vay trên giá trị TSBĐ — lưu SCD1</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>A.LOAN_TO_VALUE</t>
         </is>
       </c>
-      <c r="F42" s="31" t="n"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="44" t="inlineStr">
+      <c r="F43" s="30" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>LOAN_OBJECTIVE</t>
         </is>
       </c>
-      <c r="B43" s="27" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C43" s="31" t="inlineStr">
+      <c r="C44" s="30" t="inlineStr">
         <is>
           <t>Mục đích vay</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>Mục đích vay — lưu SCD1</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>A.LOAN_OBJECTIVE</t>
         </is>
       </c>
-      <c r="F43" s="31" t="n"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="44" t="inlineStr">
+      <c r="F44" s="30" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="36" t="inlineStr">
         <is>
           <t>TOTAL_INCOME</t>
         </is>
       </c>
-      <c r="B44" s="27" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C44" s="31" t="inlineStr">
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>Tổng thu nhập khách hàng</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Tổng thu nhập khách hàng — lưu SCD1</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>A.TOTAL_INCOME</t>
         </is>
       </c>
-      <c r="F44" s="31" t="n"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="44" t="inlineStr">
+      <c r="F45" s="30" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>SALARYFLAG</t>
         </is>
       </c>
-      <c r="B45" s="27" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C45" s="31" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu từ lương</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu từ lương hay không — lưu SCD1</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>A.SALARYFLAG</t>
         </is>
       </c>
-      <c r="F45" s="31" t="n"/>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="44" t="inlineStr">
+      <c r="F46" s="30" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="36" t="inlineStr">
         <is>
           <t>CARFLAG</t>
         </is>
       </c>
-      <c r="B46" s="27" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C46" s="31" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu thuê phương tiện</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu từ cho thuê phương tiện hay không — lưu SCD1</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>A.CARFLAG</t>
         </is>
       </c>
-      <c r="F46" s="31" t="n"/>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="44" t="inlineStr">
+      <c r="F47" s="30" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>HOUSEFLAG</t>
         </is>
       </c>
-      <c r="B47" s="27" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C47" s="31" t="inlineStr">
+      <c r="C48" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu thuê nhà</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu từ cho thuê nhà hay không — lưu SCD1</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>A.HOUSEFLAG</t>
         </is>
       </c>
-      <c r="F47" s="31" t="n"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="44" t="inlineStr">
+      <c r="F48" s="30" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>ENTERPRISSEFLAG</t>
         </is>
       </c>
-      <c r="B48" s="27" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C48" s="31" t="inlineStr">
+      <c r="C49" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu lợi nhuận DN</t>
         </is>
       </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu từ lợi nhuận doanh nghiệp hay không — lưu SCD1 (giữ nguyên tên sai chính tả nguồn)</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>A.ENTERPRISSEFLAG</t>
         </is>
       </c>
-      <c r="F48" s="31" t="n"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="44" t="inlineStr">
+      <c r="F49" s="30" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>DIVINGFLAG</t>
         </is>
       </c>
-      <c r="B49" s="27" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C49" s="31" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu cổ tức</t>
         </is>
       </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu từ cổ tức hay không — lưu SCD1 (giữ nguyên tên sai chính tả nguồn)</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>A.DIVINGFLAG</t>
         </is>
       </c>
-      <c r="F49" s="31" t="n"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="44" t="inlineStr">
+      <c r="F50" s="30" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="36" t="inlineStr">
         <is>
           <t>FAIMILYFLAG</t>
         </is>
       </c>
-      <c r="B50" s="27" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C50" s="31" t="inlineStr">
+      <c r="C51" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu kinh doanh hộ GĐ</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu từ kinh doanh hộ gia đình hay không — lưu SCD1 (giữ nguyên tên sai chính tả nguồn)</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>A.FAIMILYFLAG</t>
         </is>
       </c>
-      <c r="F50" s="31" t="n"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="44" t="inlineStr">
+      <c r="F51" s="30" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>NONLICFLAG</t>
         </is>
       </c>
-      <c r="B51" s="27" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C51" s="31" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu KD không đăng ký</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu từ kinh doanh không đăng ký hay không — lưu SCD1</t>
         </is>
       </c>
-      <c r="E51" s="17" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>A.NONLICFLAG</t>
         </is>
       </c>
-      <c r="F51" s="31" t="n"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="44" t="inlineStr">
+      <c r="F52" s="30" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>WAGESFLAG</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C52" s="31" t="inlineStr">
+      <c r="C53" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu tiền công</t>
         </is>
       </c>
-      <c r="D52" s="17" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu từ tiền công hay không — lưu SCD1</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>A.WAGESFLAG</t>
         </is>
       </c>
-      <c r="F52" s="31" t="n"/>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="44" t="inlineStr">
+      <c r="F53" s="30" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>PENSIONFLAG</t>
         </is>
       </c>
-      <c r="B53" s="27" t="inlineStr">
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C53" s="31" t="inlineStr">
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu lương hưu</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu từ lương hưu/phụ cấp hay không — lưu SCD1</t>
         </is>
       </c>
-      <c r="E53" s="17" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
         <is>
           <t>A.PENSIONFLAG</t>
         </is>
       </c>
-      <c r="F53" s="31" t="n"/>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="44" t="inlineStr">
+      <c r="F54" s="30" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="36" t="inlineStr">
         <is>
           <t>OTHERFLAG</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C54" s="31" t="inlineStr">
+      <c r="C55" s="30" t="inlineStr">
         <is>
           <t>Nguồn thu khác</t>
         </is>
       </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>Có nguồn thu khác hay không — lưu SCD1</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>A.OTHERFLAG</t>
         </is>
       </c>
-      <c r="F54" s="31" t="n"/>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="44" t="inlineStr">
+      <c r="F55" s="30" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>PRODUCT_NAME</t>
         </is>
       </c>
-      <c r="B55" s="27" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C55" s="31" t="inlineStr">
+      <c r="C56" s="30" t="inlineStr">
         <is>
           <t>Tên sản phẩm vay</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>Tên sản phẩm vay</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>A.PRODUCT_NAME</t>
         </is>
       </c>
-      <c r="F55" s="31" t="n"/>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="44" t="inlineStr">
+      <c r="F56" s="30" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="36" t="inlineStr">
         <is>
           <t>C_PHONE_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="B56" s="27" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C56" s="31" t="inlineStr">
+      <c r="C57" s="30" t="inlineStr">
         <is>
           <t>Cờ phát sinh Xác minh ĐT</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>Cờ đánh dấu hồ sơ có phát sinh nhánh phụ Xác minh điện thoại — lưu SCD1</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>A.C_PHONE_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="F56" s="31" t="n"/>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="44" t="inlineStr">
+      <c r="F57" s="30" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>C_PHONE_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="B57" s="27" t="inlineStr">
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C57" s="31" t="inlineStr">
+      <c r="C58" s="30" t="inlineStr">
         <is>
           <t>Cờ xóa nhánh Xác minh ĐT</t>
         </is>
       </c>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>Cờ đánh dấu nhánh phụ Xác minh điện thoại đã được xóa/hủy — lưu SCD1</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>A.C_PHONE_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="F57" s="31" t="n"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="44" t="inlineStr">
+      <c r="F58" s="30" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="36" t="inlineStr">
         <is>
           <t>C_FI_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="B58" s="27" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C58" s="31" t="inlineStr">
+      <c r="C59" s="30" t="inlineStr">
         <is>
           <t>Cờ phát sinh Thẩm định thực địa</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>Cờ đánh dấu hồ sơ có phát sinh nhánh phụ Thẩm định thực địa — lưu SCD1</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr">
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>A.C_FI_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="F58" s="31" t="n"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="44" t="inlineStr">
+      <c r="F59" s="30" t="n"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>C_FI_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="B59" s="27" t="inlineStr">
+      <c r="B60" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C59" s="31" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>Cờ xóa nhánh Thẩm định thực địa</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>Cờ đánh dấu nhánh phụ Thẩm định thực địa đã được xóa/hủy — lưu SCD1</t>
         </is>
       </c>
-      <c r="E59" s="17" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
         <is>
           <t>A.C_FI_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="F59" s="31" t="n"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="44" t="inlineStr">
+      <c r="F60" s="30" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>C_LEGAL_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="B60" s="27" t="inlineStr">
+      <c r="B61" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C60" s="31" t="inlineStr">
+      <c r="C61" s="30" t="inlineStr">
         <is>
           <t>Cờ phát sinh Thẩm định pháp chế</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Cờ đánh dấu hồ sơ có phát sinh nhánh phụ Thẩm định pháp chế — lưu SCD1</t>
         </is>
       </c>
-      <c r="E60" s="17" t="inlineStr">
+      <c r="E61" s="17" t="inlineStr">
         <is>
           <t>A.C_LEGAL_CREATE_FLAG</t>
         </is>
       </c>
-      <c r="F60" s="31" t="n"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="44" t="inlineStr">
+      <c r="F61" s="30" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>C_LEGAL_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="B61" s="27" t="inlineStr">
+      <c r="B62" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C61" s="31" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>Cờ xóa nhánh Thẩm định pháp chế</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Cờ đánh dấu nhánh phụ Thẩm định pháp chế đã được xóa/hủy — lưu SCD1</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>A.C_LEGAL_DELETE_FLAG</t>
         </is>
       </c>
-      <c r="F61" s="31" t="n"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="44" t="inlineStr">
+      <c r="F62" s="30" t="n"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="36" t="inlineStr">
         <is>
           <t>REINITIATE</t>
         </is>
       </c>
-      <c r="B62" s="27" t="inlineStr">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(5)</t>
         </is>
       </c>
-      <c r="C62" s="31" t="inlineStr">
+      <c r="C63" s="30" t="inlineStr">
         <is>
           <t>Cờ khởi tạo lại</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>Cờ đánh dấu hồ sơ đang ở luồng khởi tạo lại (ReInitiate) sau khi bị từ chối — lưu SCD1</t>
         </is>
       </c>
-      <c r="E62" s="17" t="inlineStr">
+      <c r="E63" s="17" t="inlineStr">
         <is>
           <t>A.REINITIATE</t>
         </is>
       </c>
-      <c r="F62" s="31" t="n"/>
-    </row>
-    <row r="63" ht="17" customFormat="1" customHeight="1" s="15">
-      <c r="A63" s="44" t="inlineStr">
+      <c r="F63" s="30" t="n"/>
+    </row>
+    <row r="64" ht="30" customFormat="1" customHeight="1" s="15">
+      <c r="A64" s="36" t="inlineStr">
         <is>
           <t>NORMALBRHOLD</t>
         </is>
       </c>
-      <c r="B63" s="27" t="inlineStr">
+      <c r="B64" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C63" s="31" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>Cờ hold ký HĐ không công chứng</t>
         </is>
       </c>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>Cờ tạm giữ (hold) hồ sơ tại bước ký hợp đồng, hồ sơ không công chứng — lưu SCD1</t>
         </is>
       </c>
-      <c r="E63" s="17" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>A.NORMALBRHOLD</t>
         </is>
       </c>
-      <c r="F63" s="31" t="n"/>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="44" t="inlineStr">
+      <c r="F64" s="30" t="n"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="36" t="inlineStr">
         <is>
           <t>REGBRHOLD</t>
         </is>
       </c>
-      <c r="B64" s="27" t="inlineStr">
+      <c r="B65" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C64" s="31" t="inlineStr">
+      <c r="C65" s="30" t="inlineStr">
         <is>
           <t>Cờ hold ký HĐ có công chứng</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>Cờ tạm giữ (hold) hồ sơ tại bước ký hợp đồng, hồ sơ có công chứng — lưu SCD1</t>
         </is>
       </c>
-      <c r="E64" s="17" t="inlineStr">
+      <c r="E65" s="17" t="inlineStr">
         <is>
           <t>A.REGBRHOLD</t>
         </is>
       </c>
-      <c r="F64" s="31" t="n"/>
-    </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="44" t="inlineStr">
+      <c r="F65" s="30" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="36" t="inlineStr">
         <is>
           <t>STP_FLAG</t>
         </is>
       </c>
-      <c r="B65" s="27" t="inlineStr">
+      <c r="B66" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C65" s="31" t="inlineStr">
+      <c r="C66" s="30" t="inlineStr">
         <is>
           <t>Cờ xử lý tự động STP</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>Cờ xử lý tự động (Straight-Through Processing) — lưu SCD1</t>
         </is>
       </c>
-      <c r="E65" s="17" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>A.STP_FLAG</t>
         </is>
       </c>
-      <c r="F65" s="31" t="n"/>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="44" t="inlineStr">
+      <c r="F66" s="30" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="36" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="B66" s="27" t="inlineStr">
+      <c r="B67" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C66" s="31" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>Cờ đủ điều kiện</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>Cờ đủ điều kiện — lưu SCD1</t>
         </is>
       </c>
-      <c r="E66" s="17" t="inlineStr">
+      <c r="E67" s="17" t="inlineStr">
         <is>
           <t>A.ELIGIBLE</t>
         </is>
       </c>
-      <c r="F66" s="31" t="n"/>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="44" t="inlineStr">
+      <c r="F67" s="30" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>TOTALNONELIGIBLE</t>
         </is>
       </c>
-      <c r="B67" s="27" t="inlineStr">
+      <c r="B68" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(5)</t>
         </is>
       </c>
-      <c r="C67" s="31" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>Số điều kiện không đạt</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>Số lượng điều kiện không đủ tiêu chuẩn ghi nhận trên hồ sơ — lưu SCD1</t>
         </is>
       </c>
-      <c r="E67" s="17" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>A.TOTALNONELIGIBLE</t>
         </is>
       </c>
-      <c r="F67" s="31" t="n"/>
-    </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="44" t="inlineStr">
+      <c r="F68" s="30" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="36" t="inlineStr">
         <is>
           <t>CANCEL_REASON</t>
         </is>
       </c>
-      <c r="B68" s="27" t="inlineStr">
+      <c r="B69" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C68" s="31" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>Lý do hủy hồ sơ</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Lý do hủy hồ sơ — lưu SCD1</t>
         </is>
       </c>
-      <c r="E68" s="17" t="inlineStr">
+      <c r="E69" s="17" t="inlineStr">
         <is>
           <t>A.CANCEL_REASON</t>
         </is>
       </c>
-      <c r="F68" s="31" t="n"/>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="44" t="inlineStr">
+      <c r="F69" s="30" t="n"/>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="36" t="inlineStr">
         <is>
           <t>EFF_DATE</t>
         </is>
       </c>
-      <c r="B69" s="27" t="inlineStr">
+      <c r="B70" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C69" s="31" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>Ngày hiệu lực bản ghi</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>Ngày bắt đầu hiệu lực của phiên bản bản ghi (SCD Type 2)</t>
         </is>
       </c>
-      <c r="E69" s="17" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>A.EFF_DATE</t>
         </is>
       </c>
-      <c r="F69" s="31" t="n"/>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="44" t="inlineStr">
+      <c r="F70" s="30" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="36" t="inlineStr">
         <is>
           <t>EXP_DATE</t>
         </is>
       </c>
-      <c r="B70" s="27" t="inlineStr">
+      <c r="B71" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C70" s="31" t="inlineStr">
+      <c r="C71" s="30" t="inlineStr">
         <is>
           <t>Ngày hết hiệu lực bản ghi</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>Ngày hết hiệu lực của phiên bản bản ghi; NULL = bản ghi hiện hành</t>
         </is>
       </c>
-      <c r="E70" s="17" t="inlineStr">
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <t>A.EXP_DATE</t>
         </is>
       </c>
-      <c r="F70" s="31" t="n"/>
-    </row>
-    <row r="72"/>
+      <c r="F71" s="30" t="n"/>
+    </row>
+    <row r="73"/>
   </sheetData>
-  <autoFilter ref="A5:E70"/>
+  <autoFilter ref="A6:E71"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
